--- a/artfynd/A 26934-2025 artfynd.xlsx
+++ b/artfynd/A 26934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104210968</v>
       </c>
       <c r="B2" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449872.7457023374</v>
+        <v>449873</v>
       </c>
       <c r="R2" t="n">
-        <v>6429656.784509083</v>
+        <v>6429656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-10-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>104440689</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449664.3864050148</v>
+        <v>449664</v>
       </c>
       <c r="R3" t="n">
-        <v>6429933.915504836</v>
+        <v>6429934</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -883,19 +863,9 @@
           <t>2022-04-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,6 +889,118 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72567322</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104253</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Habo-Baskarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>449834</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6429840</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-07-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-07-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Längs skogsväg mellan Baskarp Bråten och Baskarp Sand, bäckravin i skogsmark, ca 1 km SÖ om Sibbabergets topp.</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Göteborg-Herbarium GB</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Johan Rova 2898</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Rova</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Rova</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26934-2025 artfynd.xlsx
+++ b/artfynd/A 26934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104210968</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104440689</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72567322</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>